--- a/results/log_pv_cap/log_pv_cap_densities_fdensity_tests.xlsx
+++ b/results/log_pv_cap/log_pv_cap_densities_fdensity_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>82.32***</t>
+          <t>78.01***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>38.48***</t>
+          <t>42.52***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8256.27***</t>
+          <t>7894.45***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.30***</t>
+          <t>68.76***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>988.73***</t>
+          <t>630.44***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.32***</t>
+          <t>78.01***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.72***</t>
+          <t>11.76***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6890.84***</t>
+          <t>6224.33***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.88***</t>
+          <t>17.69***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>988.73***</t>
+          <t>630.44***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>82.32***</t>
+          <t>78.01***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.68***</t>
+          <t>10.25***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6869.50***</t>
+          <t>6191.07***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.33***</t>
+          <t>12.01***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>988.73***</t>
+          <t>630.44***</t>
         </is>
       </c>
     </row>
